--- a/tabela-excel/amostras.xlsx
+++ b/tabela-excel/amostras.xlsx
@@ -459,7 +459,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>101024ab</t>
+          <t>101024ad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -481,12 +481,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
     </row>
@@ -504,12 +504,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -527,12 +527,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27086</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>302</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>106184</t>
+          <t>99485</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>356</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13408</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>181</t>
         </is>
       </c>
     </row>
@@ -619,12 +619,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>370</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>823</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>121</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>273</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>282</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>290</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -878,47 +878,47 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>101024ab</t>
+          <t>101024ad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2022.000</t>
+          <t>2210.903</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12.800</t>
+          <t>21.107</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>137.000</t>
+          <t>180.389</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17762.000</t>
+          <t>18539.553</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.600</t>
+          <t>34.190</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>5250.000</t>
+          <t>4980.715</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>258.000</t>
+          <t>258.828</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35.900</t>
+          <t>60.878</t>
         </is>
       </c>
     </row>

--- a/tabela-excel/amostras.xlsx
+++ b/tabela-excel/amostras.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>101024ad</t>
+          <t>260126ab</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -481,12 +481,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>95</t>
         </is>
       </c>
     </row>
@@ -504,12 +504,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>151</t>
         </is>
       </c>
     </row>
@@ -527,12 +527,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>89091</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>303</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>240</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>99485</t>
+          <t>15004</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>143</t>
         </is>
       </c>
     </row>
@@ -619,12 +619,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>498</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>79</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>503</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>818</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>15939</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>804</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>211</t>
         </is>
       </c>
     </row>
@@ -793,31 +793,4576 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.984</t>
+          <t>11.908</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>217</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7136</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>260126ac</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2778</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10835</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>62364</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>14683</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>10123</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7695</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>10156</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3179</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>260126ad</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3728</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>15051</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>86923</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>15007</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>14608</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>10056</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>12817</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2586</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>260126ae</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>13786</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>80535</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>14493</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>13246</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>9671</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>14640</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>5406</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>6456</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>260126af</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>15075</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>84447</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>14960</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>14524</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>9568</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2393</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3876</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>7007</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>260126ag</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3977</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>15138</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>85765</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>14198</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>13948</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>9824</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>15933</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3778</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>6076</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>260126ah</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3986</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>15936</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>89839</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>14788</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>15512</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>9970</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>15390</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>5111</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>7242</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>260126ai</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>3133</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>11982</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>70809</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>13728</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>11384</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>8397</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>11863</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2474</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3820</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>6258</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>260126aj</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>4085</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>16067</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>89181</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>15561</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>15524</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>10325</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>15161</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>3282</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>4935</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>6747</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>260126ak</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>3588</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>14138</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>82313</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>14420</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>13247</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>9250</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>14928</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>5065</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>6856</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>260126al</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>4113</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>15726</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>88054</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>14872</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>15547</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>10897</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>14575</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>1161</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>3245</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>4568</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>7043</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>260126am</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2.013</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>3344</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2.307</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>12994</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2.622</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>76147</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2.957</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>13876</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>3.313</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>12077</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.691</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>8716</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>4.509</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>5.412</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>5.895</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>12963</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>6.925</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>7.472</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>8.041</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>8.631</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2976</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>11.908</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>4318</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>22.103</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2.984</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>6562</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -830,7 +5375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,47 +5423,564 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>101024ad</t>
+          <t>260126ab</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2210.903</t>
+          <t>2022.000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.107</t>
+          <t>12.800</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>180.389</t>
+          <t>137.000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18539.553</t>
+          <t>17762.000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34.190</t>
+          <t>32.600</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4980.715</t>
+          <t>5250.000</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>258.828</t>
+          <t>258.000</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60.878</t>
+          <t>35.900</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>260126ac</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1459.019</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8.056</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>85.278</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>11707.105</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>18.922</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3664.551</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>175.597</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>17.911</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>260126ad</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1865.514</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8.217</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>105.299</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>16529.205</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>19.884</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4811.554</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>238.658</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>22.614</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>260126ae</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1857.720</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12.857</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>124.541</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15519.637</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>31.279</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4744.314</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>226.352</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>31.520</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>260126af</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1780.560</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10.487</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>106.008</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16485.789</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>23.959</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4798.187</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>239.789</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20.992</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>260126ag</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1926.319</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>13.253</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>138.357</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>16681.683</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28.828</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5425.400</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>253.714</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>34.920</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>260126ah</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1876.950</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13.419</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>128.310</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>17812.031</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>26.132</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5220.729</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>256.433</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>31.317</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>260126ai</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1702.880</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8.317</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>106.541</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>14081.298</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>24.485</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4420.348</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>207.695</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>23.650</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>260126aj</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1847.224</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12.048</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>120.121</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16940.305</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>22.960</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5084.613</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>245.698</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>27.678</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>260126ak</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1785.844</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11.545</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>127.634</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15599.381</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>29.614</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4819.373</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>233.306</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30.250</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>260126al</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2039.880</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10.948</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>120.828</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>17751.388</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>32.096</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5356.642</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>251.624</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>28.634</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>260126am</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1748.719</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8.476</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>115.178</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>14779.164</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>27.314</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4667.725</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>222.834</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>28.145</t>
         </is>
       </c>
     </row>

--- a/tabela-excel/amostras.xlsx
+++ b/tabela-excel/amostras.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="63">
   <si>
     <t>290426ab</t>
   </si>
@@ -195,661 +195,7 @@
     <t>Amostra</t>
   </si>
   <si>
-    <t>0.0170</t>
-  </si>
-  <si>
-    <t>0.01300</t>
-  </si>
-  <si>
-    <t>0.01200</t>
-  </si>
-  <si>
-    <t>0.00900</t>
-  </si>
-  <si>
-    <t>0.00800</t>
-  </si>
-  <si>
-    <t>0.01000</t>
-  </si>
-  <si>
-    <t>0.01400</t>
-  </si>
-  <si>
-    <t>0.017</t>
-  </si>
-  <si>
-    <t>0.0090</t>
-  </si>
-  <si>
-    <t>0.0080</t>
-  </si>
-  <si>
-    <t>0.0060</t>
-  </si>
-  <si>
-    <t>0.0050</t>
-  </si>
-  <si>
-    <t>0.012</t>
-  </si>
-  <si>
-    <t>0.0100</t>
-  </si>
-  <si>
-    <t>0.0070</t>
-  </si>
-  <si>
-    <t>1300</t>
-  </si>
-  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>50.5</t>
-  </si>
-  <si>
-    <t>5.23</t>
-  </si>
-  <si>
-    <t>4.83</t>
-  </si>
-  <si>
-    <t>3.12</t>
-  </si>
-  <si>
-    <t>2.03</t>
-  </si>
-  <si>
-    <t>3.31</t>
-  </si>
-  <si>
-    <t>5.63</t>
-  </si>
-  <si>
-    <t>3.88</t>
-  </si>
-  <si>
-    <t>5.71</t>
-  </si>
-  <si>
-    <t>5.04</t>
-  </si>
-  <si>
-    <t>3.64</t>
-  </si>
-  <si>
-    <t>6600</t>
-  </si>
-  <si>
-    <t>4760</t>
-  </si>
-  <si>
-    <t>7597</t>
-  </si>
-  <si>
-    <t>3535</t>
-  </si>
-  <si>
-    <t>3305</t>
-  </si>
-  <si>
-    <t>4768</t>
-  </si>
-  <si>
-    <t>8733</t>
-  </si>
-  <si>
-    <t>7525</t>
-  </si>
-  <si>
-    <t>10334</t>
-  </si>
-  <si>
-    <t>10570</t>
-  </si>
-  <si>
-    <t>8363</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>0.71</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
-    <t>0.28</t>
-  </si>
-  <si>
-    <t>0.50</t>
-  </si>
-  <si>
-    <t>0.69</t>
-  </si>
-  <si>
-    <t>1.21</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>3.0</t>
-  </si>
-  <si>
-    <t>2.9</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>1.9</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>9.0</t>
-  </si>
-  <si>
-    <t>2.6</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>2443</t>
-  </si>
-  <si>
-    <t>2190</t>
-  </si>
-  <si>
-    <t>646</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>1522</t>
-  </si>
-  <si>
-    <t>2214</t>
-  </si>
-  <si>
-    <t>4323</t>
-  </si>
-  <si>
-    <t>4519</t>
-  </si>
-  <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>1344</t>
-  </si>
-  <si>
-    <t>26.8</t>
-  </si>
-  <si>
-    <t>15.62</t>
-  </si>
-  <si>
-    <t>17.3</t>
-  </si>
-  <si>
-    <t>10.75</t>
-  </si>
-  <si>
-    <t>10.51</t>
-  </si>
-  <si>
-    <t>14.83</t>
-  </si>
-  <si>
-    <t>18.6</t>
-  </si>
-  <si>
-    <t>19.0</t>
-  </si>
-  <si>
-    <t>24.8</t>
-  </si>
-  <si>
-    <t>24.1</t>
-  </si>
-  <si>
-    <t>21.9</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>1.6</t>
-  </si>
-  <si>
-    <t>1.16</t>
-  </si>
-  <si>
-    <t>1.13</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>0.90</t>
-  </si>
-  <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>1.8</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>2161</t>
-  </si>
-  <si>
-    <t>1219</t>
-  </si>
-  <si>
-    <t>1877</t>
-  </si>
-  <si>
-    <t>1179</t>
-  </si>
-  <si>
-    <t>1063</t>
-  </si>
-  <si>
-    <t>1491</t>
-  </si>
-  <si>
-    <t>2071</t>
-  </si>
-  <si>
-    <t>2080</t>
-  </si>
-  <si>
-    <t>2417</t>
-  </si>
-  <si>
-    <t>2385</t>
-  </si>
-  <si>
-    <t>1831</t>
-  </si>
-  <si>
-    <t>9600</t>
-  </si>
-  <si>
-    <t>3362</t>
-  </si>
-  <si>
-    <t>2268</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>1987</t>
-  </si>
-  <si>
-    <t>2262</t>
-  </si>
-  <si>
-    <t>2764</t>
-  </si>
-  <si>
-    <t>2530</t>
-  </si>
-  <si>
-    <t>2707</t>
-  </si>
-  <si>
-    <t>2773</t>
-  </si>
-  <si>
-    <t>2272</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>0.0003</t>
-  </si>
-  <si>
-    <t>0.00025</t>
-  </si>
-  <si>
-    <t>0.00023</t>
-  </si>
-  <si>
-    <t>0.00018</t>
-  </si>
-  <si>
-    <t>0.00016</t>
-  </si>
-  <si>
-    <t>0.00019</t>
-  </si>
-  <si>
-    <t>0.00027</t>
-  </si>
-  <si>
-    <t>0.004</t>
-  </si>
-  <si>
-    <t>0.0025</t>
-  </si>
-  <si>
-    <t>0.0022</t>
-  </si>
-  <si>
-    <t>0.0020</t>
-  </si>
-  <si>
-    <t>0.0018</t>
-  </si>
-  <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>0.0029</t>
-  </si>
-  <si>
-    <t>0.0027</t>
-  </si>
-  <si>
-    <t>0.0023</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>0.07</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>0.08</t>
-  </si>
-  <si>
-    <t>0.06</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>0.10</t>
-  </si>
-  <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>0.09</t>
-  </si>
-  <si>
-    <t>0.16</t>
-  </si>
-  <si>
-    <t>0.14</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>0.9</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>0.30</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>0.21</t>
-  </si>
-  <si>
-    <t>0.20</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>0.29</t>
-  </si>
-  <si>
-    <t>0.26</t>
-  </si>
-  <si>
-    <t>0.18</t>
-  </si>
-  <si>
-    <t>0.23</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>0.026</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>LD</t>
@@ -6818,616 +6164,616 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I2" t="s">
-        <v>114</v>
-      </c>
-      <c r="J2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K2" t="s">
-        <v>129</v>
-      </c>
-      <c r="L2" t="s">
-        <v>140</v>
-      </c>
-      <c r="M2" t="s">
-        <v>151</v>
-      </c>
-      <c r="N2" t="s">
-        <v>160</v>
-      </c>
-      <c r="O2" t="s">
-        <v>171</v>
-      </c>
-      <c r="P2" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>183</v>
-      </c>
-      <c r="R2" t="s">
-        <v>184</v>
+      <c r="B2">
+        <v>0.017</v>
+      </c>
+      <c r="C2">
+        <v>0.017</v>
+      </c>
+      <c r="D2">
+        <v>1300</v>
+      </c>
+      <c r="E2">
+        <v>50.5</v>
+      </c>
+      <c r="F2">
+        <v>6600</v>
+      </c>
+      <c r="G2">
+        <v>0.58</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>368</v>
+      </c>
+      <c r="K2">
+        <v>26.8</v>
+      </c>
+      <c r="L2">
+        <v>246</v>
+      </c>
+      <c r="M2">
+        <v>1.6</v>
+      </c>
+      <c r="N2">
+        <v>2161</v>
+      </c>
+      <c r="O2">
+        <v>9600</v>
+      </c>
+      <c r="P2">
+        <v>0.054</v>
+      </c>
+      <c r="Q2">
+        <v>85</v>
+      </c>
+      <c r="R2">
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
+      <c r="B3">
+        <v>0.013</v>
+      </c>
+      <c r="C3">
+        <v>0.008999999999999999</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H3" t="s">
-        <v>110</v>
+        <v>59</v>
+      </c>
+      <c r="E3">
+        <v>5.23</v>
+      </c>
+      <c r="F3">
+        <v>4760</v>
+      </c>
+      <c r="G3">
+        <v>0.71</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L3" t="s">
-        <v>141</v>
-      </c>
-      <c r="M3" t="s">
-        <v>152</v>
-      </c>
-      <c r="N3" t="s">
-        <v>161</v>
-      </c>
-      <c r="O3" t="s">
-        <v>172</v>
+        <v>59</v>
+      </c>
+      <c r="J3">
+        <v>2443</v>
+      </c>
+      <c r="K3">
+        <v>15.62</v>
+      </c>
+      <c r="L3">
+        <v>101</v>
+      </c>
+      <c r="M3">
+        <v>1.16</v>
+      </c>
+      <c r="N3">
+        <v>1219</v>
+      </c>
+      <c r="O3">
+        <v>3362</v>
       </c>
       <c r="P3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="R3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
+      <c r="B4">
+        <v>0.012</v>
+      </c>
+      <c r="C4">
+        <v>0.008</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" t="s">
-        <v>111</v>
+        <v>59</v>
+      </c>
+      <c r="E4">
+        <v>4.83</v>
+      </c>
+      <c r="F4">
+        <v>7597</v>
+      </c>
+      <c r="G4">
+        <v>0.54</v>
+      </c>
+      <c r="H4">
+        <v>2.9</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4" t="s">
-        <v>120</v>
-      </c>
-      <c r="K4" t="s">
-        <v>131</v>
-      </c>
-      <c r="L4" t="s">
-        <v>142</v>
-      </c>
-      <c r="M4" t="s">
-        <v>153</v>
-      </c>
-      <c r="N4" t="s">
-        <v>162</v>
-      </c>
-      <c r="O4" t="s">
-        <v>173</v>
+        <v>59</v>
+      </c>
+      <c r="J4">
+        <v>2190</v>
+      </c>
+      <c r="K4">
+        <v>17.3</v>
+      </c>
+      <c r="L4">
+        <v>115</v>
+      </c>
+      <c r="M4">
+        <v>1.13</v>
+      </c>
+      <c r="N4">
+        <v>1877</v>
+      </c>
+      <c r="O4">
+        <v>2268</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="s">
-        <v>75</v>
-      </c>
-      <c r="R4" t="s">
-        <v>115</v>
+        <v>59</v>
+      </c>
+      <c r="R4">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>69</v>
+      <c r="B5">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="C5">
+        <v>0.006</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H5" t="s">
-        <v>112</v>
+        <v>59</v>
+      </c>
+      <c r="E5">
+        <v>3.12</v>
+      </c>
+      <c r="F5">
+        <v>3535</v>
+      </c>
+      <c r="G5">
+        <v>0.45</v>
+      </c>
+      <c r="H5">
+        <v>2.5</v>
       </c>
       <c r="I5" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" t="s">
-        <v>121</v>
-      </c>
-      <c r="K5" t="s">
-        <v>132</v>
-      </c>
-      <c r="L5" t="s">
-        <v>143</v>
-      </c>
-      <c r="M5" t="s">
-        <v>154</v>
-      </c>
-      <c r="N5" t="s">
-        <v>163</v>
-      </c>
-      <c r="O5" t="s">
-        <v>174</v>
+        <v>59</v>
+      </c>
+      <c r="J5">
+        <v>646</v>
+      </c>
+      <c r="K5">
+        <v>10.75</v>
+      </c>
+      <c r="L5">
+        <v>66</v>
+      </c>
+      <c r="M5">
+        <v>0.79</v>
+      </c>
+      <c r="N5">
+        <v>1179</v>
+      </c>
+      <c r="O5">
+        <v>2015</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q5" t="s">
-        <v>75</v>
-      </c>
-      <c r="R5" t="s">
-        <v>185</v>
+        <v>59</v>
+      </c>
+      <c r="R5">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
+      <c r="B6">
+        <v>0.008</v>
+      </c>
+      <c r="C6">
+        <v>0.005</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H6" t="s">
-        <v>113</v>
+        <v>59</v>
+      </c>
+      <c r="E6">
+        <v>2.03</v>
+      </c>
+      <c r="F6">
+        <v>3305</v>
+      </c>
+      <c r="G6">
+        <v>0.28</v>
+      </c>
+      <c r="H6">
+        <v>1.9</v>
       </c>
       <c r="I6" t="s">
-        <v>75</v>
-      </c>
-      <c r="J6" t="s">
-        <v>122</v>
-      </c>
-      <c r="K6" t="s">
-        <v>133</v>
-      </c>
-      <c r="L6" t="s">
-        <v>144</v>
-      </c>
-      <c r="M6" t="s">
-        <v>104</v>
-      </c>
-      <c r="N6" t="s">
-        <v>164</v>
-      </c>
-      <c r="O6" t="s">
-        <v>175</v>
+        <v>59</v>
+      </c>
+      <c r="J6">
+        <v>364</v>
+      </c>
+      <c r="K6">
+        <v>10.51</v>
+      </c>
+      <c r="L6">
+        <v>67</v>
+      </c>
+      <c r="M6">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N6">
+        <v>1063</v>
+      </c>
+      <c r="O6">
+        <v>1987</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="R6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>70</v>
+      <c r="B7">
+        <v>0.01</v>
+      </c>
+      <c r="C7">
+        <v>0.005</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" t="s">
-        <v>103</v>
-      </c>
-      <c r="H7" t="s">
-        <v>111</v>
+        <v>59</v>
+      </c>
+      <c r="E7">
+        <v>3.31</v>
+      </c>
+      <c r="F7">
+        <v>4768</v>
+      </c>
+      <c r="G7">
+        <v>0.5</v>
+      </c>
+      <c r="H7">
+        <v>2.9</v>
       </c>
       <c r="I7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J7" t="s">
-        <v>123</v>
-      </c>
-      <c r="K7" t="s">
-        <v>134</v>
-      </c>
-      <c r="L7" t="s">
-        <v>145</v>
-      </c>
-      <c r="M7" t="s">
-        <v>155</v>
-      </c>
-      <c r="N7" t="s">
-        <v>165</v>
-      </c>
-      <c r="O7" t="s">
-        <v>176</v>
+        <v>59</v>
+      </c>
+      <c r="J7">
+        <v>1522</v>
+      </c>
+      <c r="K7">
+        <v>14.83</v>
+      </c>
+      <c r="L7">
+        <v>95</v>
+      </c>
+      <c r="M7">
+        <v>0.9</v>
+      </c>
+      <c r="N7">
+        <v>1491</v>
+      </c>
+      <c r="O7">
+        <v>2262</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q7" t="s">
-        <v>75</v>
-      </c>
-      <c r="R7" t="s">
-        <v>115</v>
+        <v>59</v>
+      </c>
+      <c r="R7">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s">
-        <v>68</v>
+      <c r="B8">
+        <v>0.013</v>
+      </c>
+      <c r="C8">
+        <v>0.008</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" t="s">
-        <v>93</v>
-      </c>
-      <c r="G8" t="s">
-        <v>104</v>
-      </c>
-      <c r="H8" t="s">
-        <v>114</v>
+        <v>59</v>
+      </c>
+      <c r="E8">
+        <v>5.63</v>
+      </c>
+      <c r="F8">
+        <v>8733</v>
+      </c>
+      <c r="G8">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
       </c>
       <c r="I8" t="s">
-        <v>75</v>
-      </c>
-      <c r="J8" t="s">
-        <v>124</v>
-      </c>
-      <c r="K8" t="s">
-        <v>135</v>
-      </c>
-      <c r="L8" t="s">
-        <v>146</v>
-      </c>
-      <c r="M8" t="s">
-        <v>156</v>
-      </c>
-      <c r="N8" t="s">
-        <v>166</v>
-      </c>
-      <c r="O8" t="s">
-        <v>177</v>
+        <v>59</v>
+      </c>
+      <c r="J8">
+        <v>2214</v>
+      </c>
+      <c r="K8">
+        <v>18.6</v>
+      </c>
+      <c r="L8">
+        <v>275</v>
+      </c>
+      <c r="M8">
+        <v>1.25</v>
+      </c>
+      <c r="N8">
+        <v>2071</v>
+      </c>
+      <c r="O8">
+        <v>2764</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q8" t="s">
-        <v>75</v>
-      </c>
-      <c r="R8" t="s">
-        <v>186</v>
+        <v>59</v>
+      </c>
+      <c r="R8">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
+      <c r="B9">
+        <v>0.012</v>
+      </c>
+      <c r="C9">
+        <v>0.012</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" t="s">
-        <v>94</v>
-      </c>
-      <c r="G9" t="s">
-        <v>105</v>
-      </c>
-      <c r="H9" t="s">
-        <v>115</v>
+        <v>59</v>
+      </c>
+      <c r="E9">
+        <v>3.88</v>
+      </c>
+      <c r="F9">
+        <v>7525</v>
+      </c>
+      <c r="G9">
+        <v>1.21</v>
+      </c>
+      <c r="H9">
+        <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>75</v>
-      </c>
-      <c r="J9" t="s">
-        <v>125</v>
-      </c>
-      <c r="K9" t="s">
-        <v>136</v>
-      </c>
-      <c r="L9" t="s">
-        <v>147</v>
-      </c>
-      <c r="M9" t="s">
-        <v>157</v>
-      </c>
-      <c r="N9" t="s">
-        <v>167</v>
-      </c>
-      <c r="O9" t="s">
-        <v>178</v>
+        <v>59</v>
+      </c>
+      <c r="J9">
+        <v>4323</v>
+      </c>
+      <c r="K9">
+        <v>19</v>
+      </c>
+      <c r="L9">
+        <v>179</v>
+      </c>
+      <c r="M9">
+        <v>1.8</v>
+      </c>
+      <c r="N9">
+        <v>2080</v>
+      </c>
+      <c r="O9">
+        <v>2530</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q9" t="s">
-        <v>75</v>
-      </c>
-      <c r="R9" t="s">
-        <v>187</v>
+        <v>59</v>
+      </c>
+      <c r="R9">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
+      <c r="B10">
+        <v>0.014</v>
+      </c>
+      <c r="C10">
+        <v>0.008999999999999999</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" t="s">
-        <v>84</v>
-      </c>
-      <c r="F10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" t="s">
-        <v>106</v>
-      </c>
-      <c r="H10" t="s">
-        <v>116</v>
+        <v>59</v>
+      </c>
+      <c r="E10">
+        <v>5.71</v>
+      </c>
+      <c r="F10">
+        <v>10334</v>
+      </c>
+      <c r="G10">
+        <v>0.99</v>
+      </c>
+      <c r="H10">
+        <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>75</v>
-      </c>
-      <c r="J10" t="s">
-        <v>126</v>
-      </c>
-      <c r="K10" t="s">
-        <v>137</v>
-      </c>
-      <c r="L10" t="s">
-        <v>148</v>
-      </c>
-      <c r="M10" t="s">
-        <v>158</v>
-      </c>
-      <c r="N10" t="s">
-        <v>168</v>
-      </c>
-      <c r="O10" t="s">
-        <v>179</v>
+        <v>59</v>
+      </c>
+      <c r="J10">
+        <v>4519</v>
+      </c>
+      <c r="K10">
+        <v>24.8</v>
+      </c>
+      <c r="L10">
+        <v>237</v>
+      </c>
+      <c r="M10">
+        <v>1.5</v>
+      </c>
+      <c r="N10">
+        <v>2417</v>
+      </c>
+      <c r="O10">
+        <v>2707</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q10" t="s">
-        <v>75</v>
-      </c>
-      <c r="R10" t="s">
-        <v>188</v>
+        <v>59</v>
+      </c>
+      <c r="R10">
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
+      <c r="B11">
+        <v>0.014</v>
+      </c>
+      <c r="C11">
+        <v>0.01</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" t="s">
-        <v>110</v>
+        <v>59</v>
+      </c>
+      <c r="E11">
+        <v>5.04</v>
+      </c>
+      <c r="F11">
+        <v>10570</v>
+      </c>
+      <c r="G11">
+        <v>0.62</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
       </c>
       <c r="I11" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" t="s">
-        <v>127</v>
-      </c>
-      <c r="K11" t="s">
-        <v>138</v>
-      </c>
-      <c r="L11" t="s">
-        <v>149</v>
-      </c>
-      <c r="M11" t="s">
-        <v>159</v>
-      </c>
-      <c r="N11" t="s">
-        <v>169</v>
-      </c>
-      <c r="O11" t="s">
-        <v>180</v>
+        <v>59</v>
+      </c>
+      <c r="J11">
+        <v>1608</v>
+      </c>
+      <c r="K11">
+        <v>24.1</v>
+      </c>
+      <c r="L11">
+        <v>172</v>
+      </c>
+      <c r="M11">
+        <v>1.3</v>
+      </c>
+      <c r="N11">
+        <v>2385</v>
+      </c>
+      <c r="O11">
+        <v>2773</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R11" t="s">
-        <v>189</v>
+        <v>59</v>
+      </c>
+      <c r="R11">
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
+      <c r="B12">
+        <v>0.013</v>
+      </c>
+      <c r="C12">
+        <v>0.007</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" t="s">
-        <v>117</v>
+        <v>59</v>
+      </c>
+      <c r="E12">
+        <v>3.64</v>
+      </c>
+      <c r="F12">
+        <v>8363</v>
+      </c>
+      <c r="G12">
+        <v>0.6</v>
+      </c>
+      <c r="H12">
+        <v>2.6</v>
       </c>
       <c r="I12" t="s">
-        <v>75</v>
-      </c>
-      <c r="J12" t="s">
-        <v>128</v>
-      </c>
-      <c r="K12" t="s">
-        <v>139</v>
-      </c>
-      <c r="L12" t="s">
-        <v>150</v>
-      </c>
-      <c r="M12" t="s">
-        <v>158</v>
-      </c>
-      <c r="N12" t="s">
-        <v>170</v>
-      </c>
-      <c r="O12" t="s">
-        <v>181</v>
+        <v>59</v>
+      </c>
+      <c r="J12">
+        <v>1344</v>
+      </c>
+      <c r="K12">
+        <v>21.9</v>
+      </c>
+      <c r="L12">
+        <v>131</v>
+      </c>
+      <c r="M12">
+        <v>1.5</v>
+      </c>
+      <c r="N12">
+        <v>1831</v>
+      </c>
+      <c r="O12">
+        <v>2272</v>
       </c>
       <c r="P12" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q12" t="s">
-        <v>75</v>
-      </c>
-      <c r="R12" t="s">
-        <v>190</v>
+        <v>59</v>
+      </c>
+      <c r="R12">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -7495,1339 +6841,1339 @@
     </row>
     <row r="2" spans="1:35">
       <c r="A2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B2">
-        <v>0.00027</v>
-      </c>
-      <c r="D2">
-        <v>0.006</v>
-      </c>
-      <c r="F2">
-        <v>13</v>
-      </c>
-      <c r="H2">
-        <v>0.05</v>
-      </c>
-      <c r="J2">
-        <v>70</v>
-      </c>
-      <c r="L2">
-        <v>0.14</v>
-      </c>
-      <c r="N2">
-        <v>1.2</v>
-      </c>
-      <c r="P2">
-        <v>1.6</v>
-      </c>
-      <c r="R2">
-        <v>9</v>
-      </c>
-      <c r="T2">
-        <v>0.08</v>
-      </c>
-      <c r="V2">
-        <v>13</v>
-      </c>
-      <c r="X2">
-        <v>0.3</v>
-      </c>
-      <c r="Z2">
-        <v>400</v>
-      </c>
-      <c r="AB2">
-        <v>170</v>
-      </c>
-      <c r="AD2">
-        <v>0.025</v>
-      </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
-      <c r="AH2">
-        <v>8</v>
+        <v>60</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" t="s">
+        <v>59</v>
+      </c>
+      <c r="P2" t="s">
+        <v>59</v>
+      </c>
+      <c r="R2" t="s">
+        <v>59</v>
+      </c>
+      <c r="T2" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" t="s">
+        <v>59</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:35">
       <c r="B3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="G3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="H3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="I3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="J3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="K3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="L3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="M3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="N3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="O3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="P3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="Q3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="R3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="S3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="T3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="U3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="V3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="W3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="X3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="Y3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="Z3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="AA3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="AB3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="AC3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="AD3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="AE3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="AF3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="AG3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
       <c r="AH3" t="s">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="AI3" t="s">
-        <v>280</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" t="s">
-        <v>198</v>
-      </c>
-      <c r="F4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" t="s">
-        <v>207</v>
-      </c>
-      <c r="H4" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" t="s">
-        <v>208</v>
-      </c>
-      <c r="J4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K4" t="s">
-        <v>214</v>
-      </c>
-      <c r="L4" t="s">
-        <v>98</v>
-      </c>
-      <c r="M4" t="s">
-        <v>224</v>
-      </c>
-      <c r="N4" t="s">
-        <v>109</v>
-      </c>
-      <c r="O4" t="s">
-        <v>229</v>
-      </c>
-      <c r="P4" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R4" t="s">
-        <v>118</v>
-      </c>
-      <c r="S4" t="s">
-        <v>185</v>
-      </c>
-      <c r="T4" t="s">
-        <v>129</v>
-      </c>
-      <c r="U4" t="s">
-        <v>240</v>
-      </c>
-      <c r="V4" t="s">
-        <v>140</v>
-      </c>
-      <c r="W4" t="s">
+      <c r="B4">
+        <v>0.017</v>
+      </c>
+      <c r="C4">
+        <v>0.0003</v>
+      </c>
+      <c r="D4">
+        <v>0.017</v>
+      </c>
+      <c r="E4">
+        <v>0.004</v>
+      </c>
+      <c r="F4">
+        <v>1300</v>
+      </c>
+      <c r="G4">
+        <v>19</v>
+      </c>
+      <c r="H4">
+        <v>50.5</v>
+      </c>
+      <c r="I4">
+        <v>0.6</v>
+      </c>
+      <c r="J4">
+        <v>6600</v>
+      </c>
+      <c r="K4">
+        <v>82</v>
+      </c>
+      <c r="L4">
+        <v>0.58</v>
+      </c>
+      <c r="M4">
+        <v>0.1</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4">
+        <v>0.8</v>
+      </c>
+      <c r="P4">
+        <v>5</v>
+      </c>
+      <c r="Q4">
+        <v>2</v>
+      </c>
+      <c r="R4">
+        <v>368</v>
+      </c>
+      <c r="S4">
+        <v>10</v>
+      </c>
+      <c r="T4">
+        <v>26.8</v>
+      </c>
+      <c r="U4">
+        <v>0.5</v>
+      </c>
+      <c r="V4">
         <v>246</v>
       </c>
-      <c r="X4" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>256</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>171</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>267</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>182</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>276</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>183</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>277</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>184</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>247</v>
+      <c r="W4">
+        <v>13</v>
+      </c>
+      <c r="X4">
+        <v>1.6</v>
+      </c>
+      <c r="Y4">
+        <v>0.3</v>
+      </c>
+      <c r="Z4">
+        <v>2161</v>
+      </c>
+      <c r="AA4">
+        <v>320</v>
+      </c>
+      <c r="AB4">
+        <v>9600</v>
+      </c>
+      <c r="AC4">
+        <v>181</v>
+      </c>
+      <c r="AD4">
+        <v>0.054</v>
+      </c>
+      <c r="AE4">
+        <v>0.026</v>
+      </c>
+      <c r="AF4">
+        <v>85</v>
+      </c>
+      <c r="AG4">
+        <v>15</v>
+      </c>
+      <c r="AH4">
+        <v>31</v>
+      </c>
+      <c r="AI4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:35">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" t="s">
-        <v>199</v>
+      <c r="B5">
+        <v>0.013</v>
+      </c>
+      <c r="C5">
+        <v>0.00025</v>
+      </c>
+      <c r="D5">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E5">
+        <v>0.0025</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I5" t="s">
-        <v>209</v>
-      </c>
-      <c r="J5" t="s">
-        <v>88</v>
-      </c>
-      <c r="K5" t="s">
-        <v>215</v>
-      </c>
-      <c r="L5" t="s">
-        <v>99</v>
-      </c>
-      <c r="M5" t="s">
-        <v>225</v>
-      </c>
-      <c r="N5" t="s">
-        <v>110</v>
-      </c>
-      <c r="O5" t="s">
-        <v>230</v>
+        <v>59</v>
+      </c>
+      <c r="H5">
+        <v>5.23</v>
+      </c>
+      <c r="I5">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J5">
+        <v>4760</v>
+      </c>
+      <c r="K5">
+        <v>59</v>
+      </c>
+      <c r="L5">
+        <v>0.71</v>
+      </c>
+      <c r="M5">
+        <v>0.11</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q5" t="s">
-        <v>75</v>
-      </c>
-      <c r="R5" t="s">
-        <v>119</v>
-      </c>
-      <c r="S5" t="s">
-        <v>233</v>
-      </c>
-      <c r="T5" t="s">
-        <v>130</v>
-      </c>
-      <c r="U5" t="s">
-        <v>241</v>
-      </c>
-      <c r="V5" t="s">
-        <v>141</v>
-      </c>
-      <c r="W5" t="s">
-        <v>247</v>
-      </c>
-      <c r="X5" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>172</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>268</v>
+        <v>59</v>
+      </c>
+      <c r="R5">
+        <v>2443</v>
+      </c>
+      <c r="S5">
+        <v>51</v>
+      </c>
+      <c r="T5">
+        <v>15.62</v>
+      </c>
+      <c r="U5">
+        <v>0.3</v>
+      </c>
+      <c r="V5">
+        <v>101</v>
+      </c>
+      <c r="W5">
+        <v>8</v>
+      </c>
+      <c r="X5">
+        <v>1.16</v>
+      </c>
+      <c r="Y5">
+        <v>0.29</v>
+      </c>
+      <c r="Z5">
+        <v>1219</v>
+      </c>
+      <c r="AA5">
+        <v>194</v>
+      </c>
+      <c r="AB5">
+        <v>3362</v>
+      </c>
+      <c r="AC5">
+        <v>87</v>
       </c>
       <c r="AD5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AE5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AF5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AG5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AH5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AI5" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:35">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" t="s">
-        <v>200</v>
+      <c r="B6">
+        <v>0.012</v>
+      </c>
+      <c r="C6">
+        <v>0.00023</v>
+      </c>
+      <c r="D6">
+        <v>0.008</v>
+      </c>
+      <c r="E6">
+        <v>0.0022</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" t="s">
-        <v>209</v>
-      </c>
-      <c r="J6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K6" t="s">
-        <v>216</v>
-      </c>
-      <c r="L6" t="s">
-        <v>100</v>
-      </c>
-      <c r="M6" t="s">
-        <v>226</v>
-      </c>
-      <c r="N6" t="s">
-        <v>111</v>
-      </c>
-      <c r="O6" t="s">
-        <v>231</v>
+        <v>59</v>
+      </c>
+      <c r="H6">
+        <v>4.83</v>
+      </c>
+      <c r="I6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J6">
+        <v>7597</v>
+      </c>
+      <c r="K6">
+        <v>83</v>
+      </c>
+      <c r="L6">
+        <v>0.54</v>
+      </c>
+      <c r="M6">
+        <v>0.09</v>
+      </c>
+      <c r="N6">
+        <v>2.9</v>
+      </c>
+      <c r="O6">
+        <v>0.9</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q6" t="s">
-        <v>75</v>
-      </c>
-      <c r="R6" t="s">
-        <v>120</v>
-      </c>
-      <c r="S6" t="s">
-        <v>217</v>
-      </c>
-      <c r="T6" t="s">
-        <v>131</v>
-      </c>
-      <c r="U6" t="s">
-        <v>242</v>
-      </c>
-      <c r="V6" t="s">
-        <v>142</v>
-      </c>
-      <c r="W6" t="s">
-        <v>247</v>
-      </c>
-      <c r="X6" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>253</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>258</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>173</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>269</v>
+        <v>59</v>
+      </c>
+      <c r="R6">
+        <v>2190</v>
+      </c>
+      <c r="S6">
+        <v>46</v>
+      </c>
+      <c r="T6">
+        <v>17.3</v>
+      </c>
+      <c r="U6">
+        <v>0.3</v>
+      </c>
+      <c r="V6">
+        <v>115</v>
+      </c>
+      <c r="W6">
+        <v>8</v>
+      </c>
+      <c r="X6">
+        <v>1.13</v>
+      </c>
+      <c r="Y6">
+        <v>0.26</v>
+      </c>
+      <c r="Z6">
+        <v>1877</v>
+      </c>
+      <c r="AA6">
+        <v>245</v>
+      </c>
+      <c r="AB6">
+        <v>2268</v>
+      </c>
+      <c r="AC6">
+        <v>71</v>
       </c>
       <c r="AD6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AE6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AF6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AG6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>249</v>
+        <v>59</v>
+      </c>
+      <c r="AH6">
+        <v>16</v>
+      </c>
+      <c r="AI6">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:35">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" t="s">
-        <v>201</v>
+      <c r="B7">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="C7">
+        <v>0.00018</v>
+      </c>
+      <c r="D7">
+        <v>0.006</v>
+      </c>
+      <c r="E7">
+        <v>0.002</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I7" t="s">
-        <v>210</v>
-      </c>
-      <c r="J7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K7" t="s">
-        <v>217</v>
-      </c>
-      <c r="L7" t="s">
-        <v>101</v>
-      </c>
-      <c r="M7" t="s">
-        <v>209</v>
-      </c>
-      <c r="N7" t="s">
-        <v>112</v>
-      </c>
-      <c r="O7" t="s">
-        <v>229</v>
+        <v>59</v>
+      </c>
+      <c r="H7">
+        <v>3.12</v>
+      </c>
+      <c r="I7">
+        <v>0.05</v>
+      </c>
+      <c r="J7">
+        <v>3535</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>0.45</v>
+      </c>
+      <c r="M7">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N7">
+        <v>2.5</v>
+      </c>
+      <c r="O7">
+        <v>0.8</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q7" t="s">
-        <v>75</v>
-      </c>
-      <c r="R7" t="s">
-        <v>121</v>
-      </c>
-      <c r="S7" t="s">
-        <v>234</v>
-      </c>
-      <c r="T7" t="s">
-        <v>132</v>
-      </c>
-      <c r="U7" t="s">
-        <v>243</v>
-      </c>
-      <c r="V7" t="s">
-        <v>143</v>
-      </c>
-      <c r="W7" t="s">
-        <v>248</v>
-      </c>
-      <c r="X7" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>243</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>259</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>270</v>
+        <v>59</v>
+      </c>
+      <c r="R7">
+        <v>646</v>
+      </c>
+      <c r="S7">
+        <v>14</v>
+      </c>
+      <c r="T7">
+        <v>10.75</v>
+      </c>
+      <c r="U7">
+        <v>0.21</v>
+      </c>
+      <c r="V7">
+        <v>66</v>
+      </c>
+      <c r="W7">
+        <v>6</v>
+      </c>
+      <c r="X7">
+        <v>0.79</v>
+      </c>
+      <c r="Y7">
+        <v>0.21</v>
+      </c>
+      <c r="Z7">
+        <v>1179</v>
+      </c>
+      <c r="AA7">
+        <v>171</v>
+      </c>
+      <c r="AB7">
+        <v>2015</v>
+      </c>
+      <c r="AC7">
+        <v>61</v>
       </c>
       <c r="AD7" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AE7" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AF7" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AG7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>185</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>232</v>
+        <v>59</v>
+      </c>
+      <c r="AH7">
+        <v>10</v>
+      </c>
+      <c r="AI7">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:35">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>202</v>
+      <c r="B8">
+        <v>0.008</v>
+      </c>
+      <c r="C8">
+        <v>0.00016</v>
+      </c>
+      <c r="D8">
+        <v>0.005</v>
+      </c>
+      <c r="E8">
+        <v>0.0018</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" t="s">
-        <v>80</v>
-      </c>
-      <c r="I8" t="s">
-        <v>211</v>
-      </c>
-      <c r="J8" t="s">
-        <v>91</v>
-      </c>
-      <c r="K8" t="s">
-        <v>218</v>
-      </c>
-      <c r="L8" t="s">
-        <v>102</v>
-      </c>
-      <c r="M8" t="s">
-        <v>210</v>
-      </c>
-      <c r="N8" t="s">
-        <v>113</v>
-      </c>
-      <c r="O8" t="s">
-        <v>208</v>
+        <v>59</v>
+      </c>
+      <c r="H8">
+        <v>2.03</v>
+      </c>
+      <c r="I8">
+        <v>0.04</v>
+      </c>
+      <c r="J8">
+        <v>3305</v>
+      </c>
+      <c r="K8">
+        <v>42</v>
+      </c>
+      <c r="L8">
+        <v>0.28</v>
+      </c>
+      <c r="M8">
+        <v>0.05</v>
+      </c>
+      <c r="N8">
+        <v>1.9</v>
+      </c>
+      <c r="O8">
+        <v>0.6</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q8" t="s">
-        <v>75</v>
-      </c>
-      <c r="R8" t="s">
-        <v>122</v>
-      </c>
-      <c r="S8" t="s">
-        <v>235</v>
-      </c>
-      <c r="T8" t="s">
-        <v>133</v>
-      </c>
-      <c r="U8" t="s">
-        <v>244</v>
-      </c>
-      <c r="V8" t="s">
-        <v>144</v>
-      </c>
-      <c r="W8" t="s">
-        <v>249</v>
-      </c>
-      <c r="X8" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>254</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>260</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>175</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>271</v>
+        <v>59</v>
+      </c>
+      <c r="R8">
+        <v>364</v>
+      </c>
+      <c r="S8">
+        <v>9</v>
+      </c>
+      <c r="T8">
+        <v>10.51</v>
+      </c>
+      <c r="U8">
+        <v>0.2</v>
+      </c>
+      <c r="V8">
+        <v>67</v>
+      </c>
+      <c r="W8">
+        <v>5</v>
+      </c>
+      <c r="X8">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Y8">
+        <v>0.18</v>
+      </c>
+      <c r="Z8">
+        <v>1063</v>
+      </c>
+      <c r="AA8">
+        <v>150</v>
+      </c>
+      <c r="AB8">
+        <v>1987</v>
+      </c>
+      <c r="AC8">
+        <v>55</v>
       </c>
       <c r="AD8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AE8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AF8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AG8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AH8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AI8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:35">
       <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>196</v>
-      </c>
-      <c r="D9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" t="s">
-        <v>200</v>
+      <c r="B9">
+        <v>0.01</v>
+      </c>
+      <c r="C9">
+        <v>0.00019</v>
+      </c>
+      <c r="D9">
+        <v>0.005</v>
+      </c>
+      <c r="E9">
+        <v>0.0022</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s">
-        <v>81</v>
-      </c>
-      <c r="I9" t="s">
-        <v>210</v>
-      </c>
-      <c r="J9" t="s">
-        <v>92</v>
-      </c>
-      <c r="K9" t="s">
-        <v>219</v>
-      </c>
-      <c r="L9" t="s">
-        <v>103</v>
-      </c>
-      <c r="M9" t="s">
-        <v>212</v>
-      </c>
-      <c r="N9" t="s">
-        <v>111</v>
-      </c>
-      <c r="O9" t="s">
-        <v>231</v>
+        <v>59</v>
+      </c>
+      <c r="H9">
+        <v>3.31</v>
+      </c>
+      <c r="I9">
+        <v>0.05</v>
+      </c>
+      <c r="J9">
+        <v>4768</v>
+      </c>
+      <c r="K9">
+        <v>57</v>
+      </c>
+      <c r="L9">
+        <v>0.5</v>
+      </c>
+      <c r="M9">
+        <v>0.08</v>
+      </c>
+      <c r="N9">
+        <v>2.9</v>
+      </c>
+      <c r="O9">
+        <v>0.9</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q9" t="s">
-        <v>75</v>
-      </c>
-      <c r="R9" t="s">
-        <v>123</v>
-      </c>
-      <c r="S9" t="s">
-        <v>188</v>
-      </c>
-      <c r="T9" t="s">
-        <v>134</v>
-      </c>
-      <c r="U9" t="s">
-        <v>102</v>
-      </c>
-      <c r="V9" t="s">
-        <v>145</v>
-      </c>
-      <c r="W9" t="s">
-        <v>250</v>
-      </c>
-      <c r="X9" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>255</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>261</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>176</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>144</v>
+        <v>59</v>
+      </c>
+      <c r="R9">
+        <v>1522</v>
+      </c>
+      <c r="S9">
+        <v>32</v>
+      </c>
+      <c r="T9">
+        <v>14.83</v>
+      </c>
+      <c r="U9">
+        <v>0.28</v>
+      </c>
+      <c r="V9">
+        <v>95</v>
+      </c>
+      <c r="W9">
+        <v>7</v>
+      </c>
+      <c r="X9">
+        <v>0.9</v>
+      </c>
+      <c r="Y9">
+        <v>0.23</v>
+      </c>
+      <c r="Z9">
+        <v>1491</v>
+      </c>
+      <c r="AA9">
+        <v>203</v>
+      </c>
+      <c r="AB9">
+        <v>2262</v>
+      </c>
+      <c r="AC9">
+        <v>67</v>
       </c>
       <c r="AD9" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AE9" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AF9" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AG9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>249</v>
+        <v>59</v>
+      </c>
+      <c r="AH9">
+        <v>16</v>
+      </c>
+      <c r="AI9">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:35">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>192</v>
-      </c>
-      <c r="D10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" t="s">
-        <v>199</v>
+      <c r="B10">
+        <v>0.013</v>
+      </c>
+      <c r="C10">
+        <v>0.00025</v>
+      </c>
+      <c r="D10">
+        <v>0.008</v>
+      </c>
+      <c r="E10">
+        <v>0.0025</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I10" t="s">
-        <v>212</v>
-      </c>
-      <c r="J10" t="s">
-        <v>93</v>
-      </c>
-      <c r="K10" t="s">
-        <v>220</v>
-      </c>
-      <c r="L10" t="s">
-        <v>104</v>
-      </c>
-      <c r="M10" t="s">
-        <v>224</v>
-      </c>
-      <c r="N10" t="s">
-        <v>114</v>
-      </c>
-      <c r="O10" t="s">
-        <v>230</v>
+        <v>59</v>
+      </c>
+      <c r="H10">
+        <v>5.63</v>
+      </c>
+      <c r="I10">
+        <v>0.08</v>
+      </c>
+      <c r="J10">
+        <v>8733</v>
+      </c>
+      <c r="K10">
+        <v>94</v>
+      </c>
+      <c r="L10">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M10">
+        <v>0.1</v>
+      </c>
+      <c r="N10">
+        <v>5</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q10" t="s">
-        <v>75</v>
-      </c>
-      <c r="R10" t="s">
-        <v>124</v>
-      </c>
-      <c r="S10" t="s">
-        <v>217</v>
-      </c>
-      <c r="T10" t="s">
-        <v>135</v>
-      </c>
-      <c r="U10" t="s">
-        <v>242</v>
-      </c>
-      <c r="V10" t="s">
-        <v>146</v>
-      </c>
-      <c r="W10" t="s">
-        <v>234</v>
-      </c>
-      <c r="X10" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>262</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>272</v>
+        <v>59</v>
+      </c>
+      <c r="R10">
+        <v>2214</v>
+      </c>
+      <c r="S10">
+        <v>46</v>
+      </c>
+      <c r="T10">
+        <v>18.6</v>
+      </c>
+      <c r="U10">
+        <v>0.3</v>
+      </c>
+      <c r="V10">
+        <v>275</v>
+      </c>
+      <c r="W10">
+        <v>14</v>
+      </c>
+      <c r="X10">
+        <v>1.25</v>
+      </c>
+      <c r="Y10">
+        <v>0.29</v>
+      </c>
+      <c r="Z10">
+        <v>2071</v>
+      </c>
+      <c r="AA10">
+        <v>274</v>
+      </c>
+      <c r="AB10">
+        <v>2764</v>
+      </c>
+      <c r="AC10">
+        <v>84</v>
       </c>
       <c r="AD10" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AE10" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AF10" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AG10" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>186</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>248</v>
+        <v>59</v>
+      </c>
+      <c r="AH10">
+        <v>21</v>
+      </c>
+      <c r="AI10">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:35">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>203</v>
+      <c r="B11">
+        <v>0.012</v>
+      </c>
+      <c r="C11">
+        <v>0.00023</v>
+      </c>
+      <c r="D11">
+        <v>0.012</v>
+      </c>
+      <c r="E11">
+        <v>0.003</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11">
+        <v>3.88</v>
+      </c>
+      <c r="I11">
+        <v>0.06</v>
+      </c>
+      <c r="J11">
+        <v>7525</v>
+      </c>
+      <c r="K11">
         <v>83</v>
       </c>
-      <c r="I11" t="s">
-        <v>213</v>
-      </c>
-      <c r="J11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K11" t="s">
-        <v>216</v>
-      </c>
-      <c r="L11" t="s">
-        <v>105</v>
-      </c>
-      <c r="M11" t="s">
-        <v>227</v>
-      </c>
-      <c r="N11" t="s">
-        <v>115</v>
-      </c>
-      <c r="O11" t="s">
-        <v>232</v>
+      <c r="L11">
+        <v>1.21</v>
+      </c>
+      <c r="M11">
+        <v>0.16</v>
+      </c>
+      <c r="N11">
+        <v>16</v>
+      </c>
+      <c r="O11">
+        <v>4</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q11" t="s">
-        <v>75</v>
-      </c>
-      <c r="R11" t="s">
-        <v>125</v>
-      </c>
-      <c r="S11" t="s">
-        <v>236</v>
-      </c>
-      <c r="T11" t="s">
-        <v>136</v>
-      </c>
-      <c r="U11" t="s">
-        <v>245</v>
-      </c>
-      <c r="V11" t="s">
-        <v>147</v>
-      </c>
-      <c r="W11" t="s">
-        <v>185</v>
-      </c>
-      <c r="X11" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>245</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>263</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>178</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>273</v>
+        <v>59</v>
+      </c>
+      <c r="R11">
+        <v>4323</v>
+      </c>
+      <c r="S11">
+        <v>89</v>
+      </c>
+      <c r="T11">
+        <v>19</v>
+      </c>
+      <c r="U11">
+        <v>0.4</v>
+      </c>
+      <c r="V11">
+        <v>179</v>
+      </c>
+      <c r="W11">
+        <v>10</v>
+      </c>
+      <c r="X11">
+        <v>1.8</v>
+      </c>
+      <c r="Y11">
+        <v>0.4</v>
+      </c>
+      <c r="Z11">
+        <v>2080</v>
+      </c>
+      <c r="AA11">
+        <v>271</v>
+      </c>
+      <c r="AB11">
+        <v>2530</v>
+      </c>
+      <c r="AC11">
+        <v>78</v>
       </c>
       <c r="AD11" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AE11" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AF11" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AG11" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>187</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>250</v>
+        <v>59</v>
+      </c>
+      <c r="AH11">
+        <v>25</v>
+      </c>
+      <c r="AI11">
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:35">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" t="s">
-        <v>204</v>
+      <c r="B12">
+        <v>0.014</v>
+      </c>
+      <c r="C12">
+        <v>0.00027</v>
+      </c>
+      <c r="D12">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E12">
+        <v>0.0029</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>75</v>
-      </c>
-      <c r="H12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" t="s">
-        <v>212</v>
-      </c>
-      <c r="J12" t="s">
-        <v>95</v>
-      </c>
-      <c r="K12" t="s">
-        <v>221</v>
-      </c>
-      <c r="L12" t="s">
-        <v>106</v>
-      </c>
-      <c r="M12" t="s">
-        <v>228</v>
-      </c>
-      <c r="N12" t="s">
-        <v>116</v>
-      </c>
-      <c r="O12" t="s">
-        <v>109</v>
+        <v>59</v>
+      </c>
+      <c r="H12">
+        <v>5.71</v>
+      </c>
+      <c r="I12">
+        <v>0.08</v>
+      </c>
+      <c r="J12">
+        <v>10334</v>
+      </c>
+      <c r="K12">
+        <v>110</v>
+      </c>
+      <c r="L12">
+        <v>0.99</v>
+      </c>
+      <c r="M12">
+        <v>0.14</v>
+      </c>
+      <c r="N12">
+        <v>9</v>
+      </c>
+      <c r="O12">
+        <v>2</v>
       </c>
       <c r="P12" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q12" t="s">
-        <v>75</v>
-      </c>
-      <c r="R12" t="s">
-        <v>126</v>
-      </c>
-      <c r="S12" t="s">
+        <v>59</v>
+      </c>
+      <c r="R12">
+        <v>4519</v>
+      </c>
+      <c r="S12">
+        <v>93</v>
+      </c>
+      <c r="T12">
+        <v>24.8</v>
+      </c>
+      <c r="U12">
+        <v>0.5</v>
+      </c>
+      <c r="V12">
         <v>237</v>
       </c>
-      <c r="T12" t="s">
-        <v>137</v>
-      </c>
-      <c r="U12" t="s">
-        <v>240</v>
-      </c>
-      <c r="V12" t="s">
-        <v>148</v>
-      </c>
-      <c r="W12" t="s">
-        <v>251</v>
-      </c>
-      <c r="X12" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>264</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>179</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>236</v>
+      <c r="W12">
+        <v>12</v>
+      </c>
+      <c r="X12">
+        <v>1.5</v>
+      </c>
+      <c r="Y12">
+        <v>0.3</v>
+      </c>
+      <c r="Z12">
+        <v>2417</v>
+      </c>
+      <c r="AA12">
+        <v>316</v>
+      </c>
+      <c r="AB12">
+        <v>2707</v>
+      </c>
+      <c r="AC12">
+        <v>89</v>
       </c>
       <c r="AD12" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AE12" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AF12" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AG12" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>188</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>247</v>
+        <v>59</v>
+      </c>
+      <c r="AH12">
+        <v>32</v>
+      </c>
+      <c r="AI12">
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:35">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" t="s">
-        <v>205</v>
+      <c r="B13">
+        <v>0.014</v>
+      </c>
+      <c r="C13">
+        <v>0.00027</v>
+      </c>
+      <c r="D13">
+        <v>0.01</v>
+      </c>
+      <c r="E13">
+        <v>0.0027</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H13" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" t="s">
-        <v>209</v>
-      </c>
-      <c r="J13" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" t="s">
-        <v>222</v>
-      </c>
-      <c r="L13" t="s">
-        <v>107</v>
-      </c>
-      <c r="M13" t="s">
-        <v>224</v>
-      </c>
-      <c r="N13" t="s">
-        <v>110</v>
-      </c>
-      <c r="O13" t="s">
-        <v>230</v>
+        <v>59</v>
+      </c>
+      <c r="H13">
+        <v>5.04</v>
+      </c>
+      <c r="I13">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J13">
+        <v>10570</v>
+      </c>
+      <c r="K13">
+        <v>112</v>
+      </c>
+      <c r="L13">
+        <v>0.62</v>
+      </c>
+      <c r="M13">
+        <v>0.1</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q13" t="s">
-        <v>75</v>
-      </c>
-      <c r="R13" t="s">
-        <v>127</v>
-      </c>
-      <c r="S13" t="s">
-        <v>238</v>
-      </c>
-      <c r="T13" t="s">
-        <v>138</v>
-      </c>
-      <c r="U13" t="s">
-        <v>240</v>
-      </c>
-      <c r="V13" t="s">
-        <v>149</v>
-      </c>
-      <c r="W13" t="s">
-        <v>185</v>
-      </c>
-      <c r="X13" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>265</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>180</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>274</v>
+        <v>59</v>
+      </c>
+      <c r="R13">
+        <v>1608</v>
+      </c>
+      <c r="S13">
+        <v>34</v>
+      </c>
+      <c r="T13">
+        <v>24.1</v>
+      </c>
+      <c r="U13">
+        <v>0.5</v>
+      </c>
+      <c r="V13">
+        <v>172</v>
+      </c>
+      <c r="W13">
+        <v>10</v>
+      </c>
+      <c r="X13">
+        <v>1.3</v>
+      </c>
+      <c r="Y13">
+        <v>0.3</v>
+      </c>
+      <c r="Z13">
+        <v>2385</v>
+      </c>
+      <c r="AA13">
+        <v>309</v>
+      </c>
+      <c r="AB13">
+        <v>2773</v>
+      </c>
+      <c r="AC13">
+        <v>88</v>
       </c>
       <c r="AD13" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AE13" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AF13" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AG13" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>189</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>248</v>
+        <v>59</v>
+      </c>
+      <c r="AH13">
+        <v>18</v>
+      </c>
+      <c r="AI13">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:35">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>192</v>
-      </c>
-      <c r="D14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" t="s">
-        <v>206</v>
+      <c r="B14">
+        <v>0.013</v>
+      </c>
+      <c r="C14">
+        <v>0.00025</v>
+      </c>
+      <c r="D14">
+        <v>0.007</v>
+      </c>
+      <c r="E14">
+        <v>0.0023</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" t="s">
-        <v>213</v>
-      </c>
-      <c r="J14" t="s">
-        <v>97</v>
-      </c>
-      <c r="K14" t="s">
-        <v>223</v>
-      </c>
-      <c r="L14" t="s">
-        <v>108</v>
-      </c>
-      <c r="M14" t="s">
-        <v>224</v>
-      </c>
-      <c r="N14" t="s">
-        <v>117</v>
-      </c>
-      <c r="O14" t="s">
-        <v>231</v>
+        <v>59</v>
+      </c>
+      <c r="H14">
+        <v>3.64</v>
+      </c>
+      <c r="I14">
+        <v>0.06</v>
+      </c>
+      <c r="J14">
+        <v>8363</v>
+      </c>
+      <c r="K14">
+        <v>91</v>
+      </c>
+      <c r="L14">
+        <v>0.6</v>
+      </c>
+      <c r="M14">
+        <v>0.1</v>
+      </c>
+      <c r="N14">
+        <v>2.6</v>
+      </c>
+      <c r="O14">
+        <v>0.9</v>
       </c>
       <c r="P14" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="Q14" t="s">
-        <v>75</v>
-      </c>
-      <c r="R14" t="s">
-        <v>128</v>
-      </c>
-      <c r="S14" t="s">
-        <v>239</v>
-      </c>
-      <c r="T14" t="s">
-        <v>139</v>
-      </c>
-      <c r="U14" t="s">
-        <v>245</v>
-      </c>
-      <c r="V14" t="s">
-        <v>150</v>
-      </c>
-      <c r="W14" t="s">
-        <v>247</v>
-      </c>
-      <c r="X14" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>242</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>170</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>266</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>181</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>275</v>
+        <v>59</v>
+      </c>
+      <c r="R14">
+        <v>1344</v>
+      </c>
+      <c r="S14">
+        <v>29</v>
+      </c>
+      <c r="T14">
+        <v>21.9</v>
+      </c>
+      <c r="U14">
+        <v>0.4</v>
+      </c>
+      <c r="V14">
+        <v>131</v>
+      </c>
+      <c r="W14">
+        <v>8</v>
+      </c>
+      <c r="X14">
+        <v>1.5</v>
+      </c>
+      <c r="Y14">
+        <v>0.3</v>
+      </c>
+      <c r="Z14">
+        <v>1831</v>
+      </c>
+      <c r="AA14">
+        <v>248</v>
+      </c>
+      <c r="AB14">
+        <v>2272</v>
+      </c>
+      <c r="AC14">
+        <v>76</v>
       </c>
       <c r="AD14" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AE14" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AF14" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="AG14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>190</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>250</v>
+        <v>59</v>
+      </c>
+      <c r="AH14">
+        <v>23</v>
+      </c>
+      <c r="AI14">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
